--- a/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0001T0006Z000C1N24_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0001T0006Z000C1N24_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>45.46008226266055</v>
+        <v>7.38726336768234</v>
       </c>
       <c r="D2" t="n">
-        <v>46.16698892489858</v>
+        <v>7.50213570029602</v>
       </c>
       <c r="E2" t="n">
-        <v>9.789663099842599</v>
+        <v>1.590820253724423</v>
       </c>
       <c r="F2" t="n">
-        <v>9.674001985725123</v>
+        <v>1.572025322680333</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>27.8176227204059</v>
+        <v>4.520363692065958</v>
       </c>
       <c r="D3" t="n">
-        <v>28.01410816045331</v>
+        <v>4.552292576073663</v>
       </c>
       <c r="E3" t="n">
-        <v>9.789663099842599</v>
+        <v>1.590820253724423</v>
       </c>
       <c r="F3" t="n">
-        <v>9.674001985725123</v>
+        <v>1.572025322680333</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>19.83501718875283</v>
+        <v>3.223190293172336</v>
       </c>
       <c r="D4" t="n">
-        <v>36.60860129744478</v>
+        <v>5.948897710834776</v>
       </c>
       <c r="E4" t="n">
-        <v>9.789663099842599</v>
+        <v>1.590820253724423</v>
       </c>
       <c r="F4" t="n">
-        <v>9.674001985725123</v>
+        <v>1.572025322680333</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>23.397362178829</v>
+        <v>3.802071354059713</v>
       </c>
       <c r="D5" t="n">
-        <v>31.69620195315855</v>
+        <v>5.150632817388264</v>
       </c>
       <c r="E5" t="n">
-        <v>9.789663099842599</v>
+        <v>1.590820253724423</v>
       </c>
       <c r="F5" t="n">
-        <v>9.674001985725123</v>
+        <v>1.572025322680333</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>14.05377296696035</v>
+        <v>2.283738107131056</v>
       </c>
       <c r="D6" t="n">
-        <v>14.09632595334244</v>
+        <v>2.290652967418146</v>
       </c>
       <c r="E6" t="n">
-        <v>9.789663099842599</v>
+        <v>1.590820253724423</v>
       </c>
       <c r="F6" t="n">
-        <v>9.674001985725123</v>
+        <v>1.572025322680333</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>28.70436810484571</v>
+        <v>4.664459817037428</v>
       </c>
       <c r="D7" t="n">
-        <v>28.77317898381017</v>
+        <v>4.675641584869153</v>
       </c>
       <c r="E7" t="n">
-        <v>9.789663099842599</v>
+        <v>1.590820253724423</v>
       </c>
       <c r="F7" t="n">
-        <v>9.674001985725123</v>
+        <v>1.572025322680333</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
